--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/CodeSystem-jp-genderedsiblingorder-cs.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/CodeSystem-jp-genderedsiblingorder-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_GenderedSiblingOrder_CS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_GenderedSiblingOrder_CS</t>
   </si>
   <si>
     <t>Version</t>
